--- a/覆盖率实验.xlsx
+++ b/覆盖率实验.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\Python\割草机导航\相机处理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDC6D86-8800-4A75-A74E-A430D90E960B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A9916A-2CAE-4C09-AD62-B8C761C6B05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{BB1149EE-BC81-4179-8825-480AF37C55DD}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
   <si>
     <t>实验序号</t>
   </si>
@@ -44,9 +44,6 @@
   </si>
   <si>
     <t>B (视觉+原始)</t>
-  </si>
-  <si>
-    <t>C (视觉+改进)</t>
   </si>
   <si>
     <t>区域覆盖率</t>
@@ -145,6 +142,18 @@
   <si>
     <t>旧版的</t>
     <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>D(融合+原始)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>C (视觉+改进)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>成功率</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -506,7 +515,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -677,19 +686,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -755,6 +751,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -887,7 +907,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -912,88 +932,118 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="15" xfId="42" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="16" xfId="42" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1351,27 +1401,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E43E82C4-08CF-414A-9FF9-5A529D6339BA}">
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.4140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.58203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.4140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.9140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.58203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.58203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11" style="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.25" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" customWidth="1"/>
+    <col min="4" max="4" width="12.4140625" customWidth="1"/>
+    <col min="5" max="6" width="12.58203125" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.4140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.9140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.58203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" style="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.25" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1385,96 +1435,102 @@
         <v>3</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="P1" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" s="5" t="s">
+      <c r="Q1" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="P1" s="28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="30">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="18">
+        <v>4</v>
+      </c>
+      <c r="C2" s="17">
         <v>0.78100000000000003</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="25">
         <v>0.80100000000000005</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="18">
         <v>0.76100000000000001</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="18">
+        <v>0.91400000000000003</v>
+      </c>
+      <c r="G2" s="24">
         <v>1</v>
       </c>
-      <c r="G2" s="6">
+      <c r="H2" s="6">
         <v>1780476637.7119999</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="4">
+      <c r="K2" s="4">
         <v>1</v>
       </c>
-      <c r="K2" s="6">
+      <c r="L2" s="6">
         <v>89.39</v>
       </c>
-      <c r="L2" s="4">
+      <c r="M2" s="4">
         <v>154458</v>
       </c>
-      <c r="M2" s="4">
+      <c r="N2" s="4">
         <v>172800</v>
       </c>
-      <c r="N2" s="5">
+      <c r="O2" s="5">
         <v>722.7</v>
       </c>
-      <c r="O2" s="28">
+      <c r="P2" s="27">
         <v>0.42399999999999999</v>
       </c>
-      <c r="P2" s="28">
+      <c r="Q2" s="27">
         <v>0.443</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
       <c r="B3" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <f>1+1+1</f>
@@ -1486,92 +1542,98 @@
       <c r="E3" s="12">
         <v>3</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="12">
+        <v>5</v>
+      </c>
+      <c r="G3" s="24">
         <v>2</v>
       </c>
-      <c r="G3" s="6">
+      <c r="H3" s="6">
         <v>1780478348.4530001</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="4">
+      <c r="K3" s="4">
         <v>1</v>
       </c>
-      <c r="K3" s="6">
+      <c r="L3" s="6">
         <v>90.22</v>
       </c>
-      <c r="L3" s="4">
+      <c r="M3" s="4">
         <v>155892</v>
       </c>
-      <c r="M3" s="4">
+      <c r="N3" s="4">
         <v>172800</v>
       </c>
-      <c r="N3" s="5">
+      <c r="O3" s="5">
         <v>514.5</v>
       </c>
-      <c r="O3" s="28">
+      <c r="P3" s="27">
         <v>0.40300000000000002</v>
       </c>
-      <c r="P3" s="28">
+      <c r="Q3" s="27">
         <v>0.47</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="31"/>
       <c r="B4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="16">
+        <v>6</v>
+      </c>
+      <c r="C4" s="15">
         <v>0.53500000000000003</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="15">
         <v>0.55500000000000005</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="20">
         <v>0.45500000000000002</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="20">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="G4" s="24">
         <v>3</v>
       </c>
-      <c r="G4" s="6">
+      <c r="H4" s="6">
         <v>1780489544.655</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="4">
+      <c r="K4" s="4">
         <v>1</v>
       </c>
-      <c r="K4" s="6">
+      <c r="L4" s="6">
         <v>88.3</v>
       </c>
-      <c r="L4" s="4">
+      <c r="M4" s="4">
         <v>152585</v>
       </c>
-      <c r="M4" s="4">
+      <c r="N4" s="4">
         <v>172800</v>
       </c>
-      <c r="N4" s="5">
+      <c r="O4" s="5">
         <v>554.5</v>
       </c>
-      <c r="O4" s="28">
+      <c r="P4" s="27">
         <v>0.34300000000000003</v>
       </c>
-      <c r="P4" s="28">
+      <c r="Q4" s="27">
         <v>0.46300000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="31"/>
       <c r="B5" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>41.73</v>
@@ -1582,143 +1644,150 @@
       <c r="E5" s="12">
         <v>35.07</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="12">
+        <v>50.41</v>
+      </c>
+      <c r="G5" s="24">
         <v>4</v>
       </c>
-      <c r="G5" s="6">
+      <c r="H5" s="6">
         <v>1780638632.1289999</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="4">
+      <c r="K5" s="4">
         <v>1</v>
       </c>
-      <c r="K5" s="6">
+      <c r="L5" s="6">
         <v>90.03</v>
       </c>
-      <c r="L5" s="4">
+      <c r="M5" s="4">
         <v>155566</v>
       </c>
-      <c r="M5" s="4">
+      <c r="N5" s="4">
         <v>172800</v>
       </c>
-      <c r="N5" s="5">
+      <c r="O5" s="5">
         <v>570.5</v>
       </c>
-      <c r="O5" s="28">
+      <c r="P5" s="27">
         <v>0.439</v>
       </c>
-      <c r="P5" s="28">
+      <c r="Q5" s="27">
         <v>0.499</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="32"/>
-      <c r="B6" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="14">
+      <c r="B6" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="13">
         <v>505.5</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="26">
         <v>639.20000000000005</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="14">
         <v>640.6</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="14">
+        <v>673.4</v>
+      </c>
+      <c r="G6" s="24">
         <v>5</v>
       </c>
-      <c r="G6" s="6">
+      <c r="H6" s="6">
         <v>1780639418.529</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="4">
+      <c r="K6" s="4">
         <v>1</v>
       </c>
-      <c r="K6" s="6">
+      <c r="L6" s="6">
         <v>88.23</v>
       </c>
-      <c r="L6" s="4">
+      <c r="M6" s="4">
         <v>152464</v>
       </c>
-      <c r="M6" s="4">
+      <c r="N6" s="4">
         <v>172800</v>
       </c>
-      <c r="N6" s="5">
+      <c r="O6" s="5">
         <v>522.5</v>
       </c>
-      <c r="O6" s="28">
+      <c r="P6" s="27">
         <v>0.46600000000000003</v>
       </c>
-      <c r="P6" s="28">
+      <c r="Q6" s="27">
         <v>0.51300000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="30">
         <f>A2+1</f>
         <v>2</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="18">
+        <v>4</v>
+      </c>
+      <c r="C7" s="17">
         <v>0.877</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <v>0.63100000000000001</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="18">
         <v>0.82399999999999995</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="18"/>
+      <c r="G7" s="24">
         <v>6</v>
       </c>
-      <c r="G7" s="6">
+      <c r="H7" s="6">
         <v>1780643877.55</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="I7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="4">
+        <v>18</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="4">
         <v>1</v>
       </c>
-      <c r="K7" s="6">
+      <c r="L7" s="6">
         <v>89.12</v>
       </c>
-      <c r="L7" s="4">
+      <c r="M7" s="4">
         <v>153992</v>
       </c>
-      <c r="M7" s="4">
+      <c r="N7" s="4">
         <v>172800</v>
       </c>
-      <c r="N7" s="5">
+      <c r="O7" s="5">
         <v>636.6</v>
       </c>
-      <c r="O7" s="28">
+      <c r="P7" s="27">
         <v>0.39500000000000002</v>
       </c>
-      <c r="P7" s="28">
+      <c r="Q7" s="27">
         <v>0.53100000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="31"/>
       <c r="B8" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <f>1+1+1+1</f>
@@ -1730,92 +1799,94 @@
       <c r="E8" s="12">
         <v>0</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="12"/>
+      <c r="G8" s="24">
         <v>7</v>
       </c>
-      <c r="G8" s="6">
+      <c r="H8" s="6">
         <v>1780644902.7</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="I8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="4">
+        <v>18</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="4">
         <v>1</v>
       </c>
-      <c r="K8" s="6">
+      <c r="L8" s="6">
         <v>90.48</v>
       </c>
-      <c r="L8" s="4">
+      <c r="M8" s="4">
         <v>156351</v>
       </c>
-      <c r="M8" s="4">
+      <c r="N8" s="4">
         <v>172800</v>
       </c>
-      <c r="N8" s="5">
+      <c r="O8" s="5">
         <v>600.6</v>
       </c>
-      <c r="O8" s="28">
+      <c r="P8" s="27">
         <v>0.41899999999999998</v>
       </c>
-      <c r="P8" s="28">
+      <c r="Q8" s="27">
         <v>0.54800000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="31"/>
       <c r="B9" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="16">
+        <v>6</v>
+      </c>
+      <c r="C9" s="15">
         <v>0.44800000000000001</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="15">
         <v>0.56899999999999995</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="20">
         <v>0.41599999999999998</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="20"/>
+      <c r="G9" s="24">
         <v>8</v>
       </c>
-      <c r="G9" s="6">
+      <c r="H9" s="6">
         <v>1780657587.8050001</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="I9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="4">
+        <v>18</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="4">
         <v>1</v>
       </c>
-      <c r="K9" s="6">
+      <c r="L9" s="6">
         <v>92.8</v>
       </c>
-      <c r="L9" s="4">
+      <c r="M9" s="4">
         <v>160354</v>
       </c>
-      <c r="M9" s="4">
+      <c r="N9" s="4">
         <v>172800</v>
       </c>
-      <c r="N9" s="5">
+      <c r="O9" s="5">
         <v>558.6</v>
       </c>
-      <c r="O9" s="28">
+      <c r="P9" s="27">
         <v>0.45900000000000002</v>
       </c>
-      <c r="P9" s="28">
+      <c r="Q9" s="27">
         <v>0.42299999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="31"/>
       <c r="B10" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>39.46</v>
@@ -1826,143 +1897,146 @@
       <c r="E10" s="12">
         <v>35.42</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="12"/>
+      <c r="G10" s="24">
         <v>9</v>
       </c>
-      <c r="G10" s="6">
+      <c r="H10" s="6">
         <v>1780658903.9449999</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="I10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="4">
+        <v>18</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="4">
         <v>1</v>
       </c>
-      <c r="K10" s="6">
+      <c r="L10" s="6">
         <v>93.79</v>
       </c>
-      <c r="L10" s="4">
+      <c r="M10" s="4">
         <v>162061</v>
       </c>
-      <c r="M10" s="4">
+      <c r="N10" s="4">
         <v>172800</v>
       </c>
-      <c r="N10" s="5">
+      <c r="O10" s="5">
         <v>586.6</v>
       </c>
-      <c r="O10" s="28">
+      <c r="P10" s="27">
         <v>0.49199999999999999</v>
       </c>
-      <c r="P10" s="28">
+      <c r="Q10" s="27">
         <v>0.41799999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="32"/>
-      <c r="B11" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="14">
+      <c r="B11" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="13">
         <v>519.9</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="13">
         <v>580.6</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="14">
         <v>474.5</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="14"/>
+      <c r="G11" s="24">
         <v>10</v>
       </c>
-      <c r="G11" s="6">
+      <c r="H11" s="6">
         <v>1780663467.3629999</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="I11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="4">
+        <v>18</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="4">
         <v>1</v>
       </c>
-      <c r="K11" s="6">
+      <c r="L11" s="6">
         <v>89.43</v>
       </c>
-      <c r="L11" s="4">
+      <c r="M11" s="4">
         <v>154538</v>
       </c>
-      <c r="M11" s="4">
+      <c r="N11" s="4">
         <v>172800</v>
       </c>
-      <c r="N11" s="5">
+      <c r="O11" s="5">
         <v>586.5</v>
       </c>
-      <c r="O11" s="28">
+      <c r="P11" s="27">
         <v>0.38700000000000001</v>
       </c>
-      <c r="P11" s="28">
+      <c r="Q11" s="27">
         <v>0.45900000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="30">
         <f>A7+1</f>
         <v>3</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="18">
+        <v>4</v>
+      </c>
+      <c r="C12" s="17">
         <v>0.65400000000000003</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="17">
         <v>0.89100000000000001</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="18">
         <v>0.73399999999999999</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="18"/>
+      <c r="G12" s="4">
         <v>11</v>
       </c>
-      <c r="G12" s="6">
+      <c r="H12" s="6">
         <v>1780732208.9449999</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="I12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" s="4">
+        <v>24</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="4">
         <v>1</v>
       </c>
-      <c r="K12" s="6">
+      <c r="L12" s="6">
         <v>95.5</v>
       </c>
-      <c r="L12" s="4">
+      <c r="M12" s="4">
         <v>165028</v>
       </c>
-      <c r="M12" s="4">
+      <c r="N12" s="4">
         <v>172800</v>
       </c>
-      <c r="N12" s="5">
+      <c r="O12" s="5">
         <v>482.4</v>
       </c>
-      <c r="O12" s="28">
+      <c r="P12" s="27">
         <v>0.22900000000000001</v>
       </c>
-      <c r="P12" s="28">
+      <c r="Q12" s="27">
         <v>0.434</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="31"/>
       <c r="B13" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <f>1+1+1+1</f>
@@ -1974,92 +2048,94 @@
       <c r="E13" s="12">
         <v>0</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="12"/>
+      <c r="G13" s="4">
         <v>12</v>
       </c>
-      <c r="G13" s="6">
+      <c r="H13" s="6">
         <v>1780733018.5020001</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="I13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" s="4">
+        <v>24</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="4">
         <v>1</v>
       </c>
-      <c r="K13" s="6">
+      <c r="L13" s="6">
         <v>98.98</v>
       </c>
-      <c r="L13" s="4">
+      <c r="M13" s="4">
         <v>171036</v>
       </c>
-      <c r="M13" s="4">
+      <c r="N13" s="4">
         <v>172800</v>
       </c>
-      <c r="N13" s="5">
+      <c r="O13" s="5">
         <v>510.5</v>
       </c>
-      <c r="O13" s="28">
+      <c r="P13" s="27">
         <v>0.26</v>
       </c>
-      <c r="P13" s="28">
+      <c r="Q13" s="27">
         <v>0.45900000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="31"/>
       <c r="B14" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="16">
+        <v>6</v>
+      </c>
+      <c r="C14" s="15">
         <v>0.53700000000000003</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="15">
         <v>0.46800000000000003</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="20">
         <v>0.46</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="20"/>
+      <c r="G14" s="4">
         <v>13</v>
       </c>
-      <c r="G14" s="6">
+      <c r="H14" s="6">
         <v>1780733949.013</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="I14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" s="4">
+        <v>24</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" s="4">
         <v>1</v>
       </c>
-      <c r="K14" s="6">
+      <c r="L14" s="6">
         <v>78.97</v>
       </c>
-      <c r="L14" s="4">
+      <c r="M14" s="4">
         <v>136465</v>
       </c>
-      <c r="M14" s="4">
+      <c r="N14" s="4">
         <v>172800</v>
       </c>
-      <c r="N14" s="5">
+      <c r="O14" s="5">
         <v>508.4</v>
       </c>
-      <c r="O14" s="28">
+      <c r="P14" s="27">
         <v>0.3</v>
       </c>
-      <c r="P14" s="28">
+      <c r="Q14" s="27">
         <v>0.46300000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="31"/>
       <c r="B15" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15">
         <v>35.130000000000003</v>
@@ -2070,77 +2146,113 @@
       <c r="E15" s="12">
         <v>34.03</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="12"/>
+      <c r="G15" s="4">
         <v>14</v>
       </c>
-      <c r="G15" s="6">
+      <c r="H15" s="6">
         <v>1780735036.589</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="I15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" s="4">
+        <v>24</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" s="4">
         <v>1</v>
       </c>
-      <c r="K15" s="6">
+      <c r="L15" s="6">
         <v>99.94</v>
       </c>
-      <c r="L15" s="4">
+      <c r="M15" s="4">
         <v>172695</v>
       </c>
-      <c r="M15" s="4">
+      <c r="N15" s="4">
         <v>172800</v>
       </c>
-      <c r="N15" s="5">
+      <c r="O15" s="5">
         <v>466.4</v>
       </c>
-      <c r="O15" s="28">
+      <c r="P15" s="27">
         <v>0.314</v>
       </c>
-      <c r="P15" s="28">
+      <c r="Q15" s="27">
         <v>0.46200000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="32"/>
-      <c r="B16" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="14">
+      <c r="B16" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="13">
         <v>520.20000000000005</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="26">
         <v>547.29999999999995</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="14">
         <v>522.20000000000005</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16" s="35"/>
+      <c r="G16" s="4">
+        <v>15</v>
+      </c>
+      <c r="H16" s="6">
+        <v>1780743171.9170001</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="4">
+        <v>1</v>
+      </c>
+      <c r="L16" s="6">
+        <v>99.81</v>
+      </c>
+      <c r="M16" s="4">
+        <v>172471</v>
+      </c>
+      <c r="N16" s="4">
+        <v>172800</v>
+      </c>
+      <c r="O16" s="5">
+        <v>580.5</v>
+      </c>
+      <c r="P16" s="27">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="Q16" s="27">
+        <v>0.38300000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="30">
         <f>A12+1</f>
         <v>4</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="18">
+        <v>4</v>
+      </c>
+      <c r="C17" s="17">
         <v>0.83899999999999997</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="17">
         <v>0.70899999999999996</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="18">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17" s="36"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="31"/>
       <c r="B18" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <f>1+1</f>
@@ -2152,28 +2264,30 @@
       <c r="E18" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18" s="35"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="31"/>
       <c r="B19" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="16">
+        <v>6</v>
+      </c>
+      <c r="C19" s="15">
         <v>0.41299999999999998</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="15">
         <v>0.627</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="20">
         <v>0.46100000000000002</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19" s="36"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="31"/>
       <c r="B20" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="17">
+        <v>7</v>
+      </c>
+      <c r="C20" s="16">
         <v>35.5</v>
       </c>
       <c r="D20">
@@ -2182,97 +2296,119 @@
       <c r="E20" s="12">
         <v>36.86</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20" s="35"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="32"/>
-      <c r="B21" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="14">
+      <c r="B21" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="13">
         <v>469.7</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="13">
         <v>586.20000000000005</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="23">
         <v>603.79999999999995</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21" s="37"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="30">
         <f>A17+1</f>
         <v>5</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="16">
+        <v>4</v>
+      </c>
+      <c r="C22" s="15">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="D22" s="15">
         <v>0.73099999999999998</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="20">
         <v>0.80200000000000005</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22" s="36"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="31"/>
       <c r="B23" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <f>1+1+1+1+1</f>
+        <v>5</v>
       </c>
       <c r="D23">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23" s="38"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="31"/>
       <c r="B24" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="16">
+        <v>6</v>
+      </c>
+      <c r="C24" s="15">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="D24" s="15">
         <v>0.53400000000000003</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="20">
         <v>0.45600000000000002</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24" s="36"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="31"/>
       <c r="B25" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25">
+        <v>42.63</v>
+      </c>
+      <c r="D25" s="16">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="E25" s="21">
+        <v>37</v>
+      </c>
+      <c r="F25" s="39"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="32"/>
+      <c r="B26" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="17">
-        <v>39.299999999999997</v>
-      </c>
-      <c r="E25" s="22">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="32"/>
-      <c r="B26" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14">
+      <c r="C26" s="13">
+        <v>580.79999999999995</v>
+      </c>
+      <c r="D26" s="13">
         <v>590.6</v>
       </c>
-      <c r="E26" s="24">
+      <c r="E26" s="23">
         <v>555.6</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="29" t="s">
-        <v>24</v>
+      <c r="F26" s="37"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="44" t="s">
+        <v>23</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" s="1" t="str">
         <f>TEXT(AVERAGE(C2,C7,C12,C17,C22),"0.0" &amp; "%") &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(C2,C7,C12,C17,C22),"0.0" &amp; "%")</f>
-        <v>78.8% ± 9.8%</v>
+        <v>80.9% ± 9.7%</v>
       </c>
       <c r="D27" s="1" t="str">
         <f>TEXT(AVERAGE(D2,D7,D12,D17,D22),"0.0" &amp; "%") &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(D2,D7,D12,D17,D22),"0.0" &amp; "%")</f>
@@ -2282,15 +2418,16 @@
         <f>TEXT(AVERAGE(E2,E7,E12,E17,E22),"0.0" &amp; "%") &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(E2,E7,E12,E17,E22),"0.0" &amp; "%")</f>
         <v>78.2% ± 3.5%</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="29"/>
+      <c r="F27" s="40"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="45"/>
       <c r="B28" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" s="1" t="str">
         <f>TEXT(AVERAGE(C3,C8,C13,C18,C23),"0.0" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(C3,C8,C13,C18,C23),"0.0")</f>
-        <v>3.3 ± 1.0</v>
+        <v>3.6 ± 1.1</v>
       </c>
       <c r="D28" s="1" t="str">
         <f>TEXT(AVERAGE(D3,D8,D13,D18,D23),"0.0" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(D3,D8,D13,D18,D23),"0.0")</f>
@@ -2300,15 +2437,16 @@
         <f>TEXT(AVERAGE(E3,E8,E13,E18,E23),"0.0" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(E3,E8,E13,E18,E23),"0.0")</f>
         <v>1.0 ± 1.4</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="29"/>
+      <c r="F28" s="40"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="45"/>
       <c r="B29" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" s="1" t="str">
         <f>TEXT(AVERAGE(C4,C9,C14,C19,C24),"0.0" &amp; "%") &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(C4,C9,C14,C19,C24),"0.0" &amp; "%")</f>
-        <v>48.3% ± 6.3%</v>
+        <v>48.2% ± 5.4%</v>
       </c>
       <c r="D29" s="1" t="str">
         <f>TEXT(AVERAGE(D4,D9,D14,D19,D24),"0.0" &amp; "%") &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(D4,D9,D14,D19,D24),"0.0" &amp; "%")</f>
@@ -2318,15 +2456,16 @@
         <f>TEXT(AVERAGE(E4,E9,E14,E19,E24),"0.0" &amp; "%") &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(E4,E9,E14,E19,E24),"0.0" &amp; "%")</f>
         <v>45.0% ± 1.9%</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="29"/>
+      <c r="F29" s="40"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="45"/>
       <c r="B30" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" s="1" t="str">
         <f>TEXT(AVERAGE(C5,C10,C15,C20,C25),"0.00" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(C5,C10,C15,C20,C25),"0.00")</f>
-        <v>37.96 ± 3.19</v>
+        <v>38.89 ± 3.46</v>
       </c>
       <c r="D30" s="1" t="str">
         <f>TEXT(AVERAGE(D5,D10,D15,D20,D25),"0.00" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(D5,D10,D15,D20,D25),"0.00")</f>
@@ -2336,15 +2475,16 @@
         <f>TEXT(AVERAGE(E5,E10,E15,E20,E25),"0.00" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(E5,E10,E15,E20,E25),"0.00")</f>
         <v>35.68 ± 1.25</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="29"/>
+      <c r="F30" s="40"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="45"/>
       <c r="B31" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" s="1" t="str">
         <f>TEXT(AVERAGE(C6,C11,C16,C21,C26),"0.0" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(C6,C11,C16,C21,C26),"0.0")</f>
-        <v>503.8 ± 23.8</v>
+        <v>519.2 ± 40.1</v>
       </c>
       <c r="D31" s="1" t="str">
         <f>TEXT(AVERAGE(D6,D11,D16,D21,D26),"0.0" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(D6,D11,D16,D21,D26),"0.0")</f>
@@ -2354,51 +2494,69 @@
         <f>TEXT(AVERAGE(E6,E11,E16,E21,E26),"0.0" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(E6,E11,E16,E21,E26),"0.0")</f>
         <v>559.3 ± 65.5</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="29"/>
+      <c r="F31" s="40"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="45"/>
       <c r="B32" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C32" t="str">
-        <f>TEXT(AVERAGE(O12:O16),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(O12:O16),"0.00%" )</f>
-        <v>27.58% ± 3.87%</v>
+        <f>TEXT(AVERAGE(P12:P16),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(P12:P16),"0.00%" )</f>
+        <v>27.40% ± 3.37%</v>
       </c>
       <c r="D32" t="str">
-        <f>TEXT(AVERAGE(O7:O11),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(O7:O11),"0.00%" )</f>
+        <f>TEXT(AVERAGE(P7:P11),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(P7:P11),"0.00%" )</f>
         <v>43.04% ± 4.44%</v>
       </c>
       <c r="E32" s="12" t="str">
-        <f>TEXT(AVERAGE(O2:O6),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(O2:O6),"0.00%" )</f>
+        <f>TEXT(AVERAGE(P2:P6),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(P2:P6),"0.00%" )</f>
         <v>41.50% ± 4.63%</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="29"/>
-      <c r="B33" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" t="str">
-        <f>TEXT(AVERAGE(P12:P16),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(P12:P16),"0.00%" )</f>
-        <v>45.45% ± 1.38%</v>
-      </c>
-      <c r="D33" s="14" t="str">
-        <f>TEXT(AVERAGE(P7:P11),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(P7:P11),"0.00%" )</f>
+      <c r="F32" s="35"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="45"/>
+      <c r="B33" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="35" t="str">
+        <f>TEXT(AVERAGE(Q12:Q16),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(Q12:Q16),"0.00%" )</f>
+        <v>44.02% ± 3.41%</v>
+      </c>
+      <c r="D33" s="35" t="str">
+        <f>TEXT(AVERAGE(Q7:Q11),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(Q7:Q11),"0.00%" )</f>
         <v>47.58% ± 6.06%</v>
       </c>
-      <c r="E33" s="15" t="str">
-        <f>TEXT(AVERAGE(P2:P6),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(P2:P6),"0.00%" )</f>
+      <c r="E33" s="12" t="str">
+        <f>TEXT(AVERAGE(Q2:Q6),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(Q2:Q6),"0.00%" )</f>
         <v>47.76% ± 2.82%</v>
+      </c>
+      <c r="F33" s="35"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="46"/>
+      <c r="B34" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="43">
+        <v>0.3</v>
+      </c>
+      <c r="D34" s="43">
+        <v>0.5</v>
+      </c>
+      <c r="E34" s="43">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A27:A33"/>
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A7:A11"/>
     <mergeCell ref="A12:A16"/>
     <mergeCell ref="A17:A21"/>
     <mergeCell ref="A22:A26"/>
+    <mergeCell ref="A27:A34"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2421,108 +2579,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="33"/>
-      <c r="B1" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
+      <c r="A1" s="28"/>
+      <c r="B1" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="33" t="s">
+      <c r="A2" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="33" t="s">
+      <c r="C2" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="33" t="s">
-        <v>30</v>
+      <c r="E2" s="28" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="34">
         <v>1</v>
       </c>
-      <c r="B3" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="35">
+      <c r="B3" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="29">
         <v>0.66049999999999998</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="29">
         <v>0.76019999999999999</v>
       </c>
-      <c r="E3" s="35">
+      <c r="E3" s="29">
         <v>0.86699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="34"/>
-      <c r="B4" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="33">
+      <c r="B4" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="28">
         <f>1+1+1+1+1+1+1+1</f>
         <v>8</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="28">
         <f>1+1</f>
         <v>2</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="34"/>
-      <c r="B5" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="35">
+      <c r="B5" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="29">
         <v>0.48149999999999998</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="29">
         <v>0.36699999999999999</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="29">
         <v>0.151</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="34"/>
-      <c r="B6" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="33">
+      <c r="B6" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="28">
         <v>31.86</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="28">
         <v>29.01</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="28">
         <v>18.190000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="34"/>
-      <c r="B7" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="33">
+      <c r="B7" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="28">
         <f>928-67-3</f>
         <v>858</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="28">
         <v>606.9</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="28">
         <f>575.3- 25-26</f>
         <v>524.29999999999995</v>
       </c>

--- a/覆盖率实验.xlsx
+++ b/覆盖率实验.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\Python\割草机导航\相机处理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A9916A-2CAE-4C09-AD62-B8C761C6B05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC5F114-99DD-44E0-A1FC-63683C6C546E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{BB1149EE-BC81-4179-8825-480AF37C55DD}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="38">
   <si>
     <t>实验序号</t>
   </si>
@@ -152,7 +152,15 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>成功率</t>
+    <t>~30%</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>~50%</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>成功率（人工估计）</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -907,7 +915,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -994,6 +1002,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1003,46 +1020,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1475,7 +1465,7 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="30">
+      <c r="A2" s="33">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -1528,7 +1518,7 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="31"/>
+      <c r="A3" s="34"/>
       <c r="B3" s="9" t="s">
         <v>5</v>
       </c>
@@ -1580,7 +1570,7 @@
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="31"/>
+      <c r="A4" s="34"/>
       <c r="B4" s="9" t="s">
         <v>6</v>
       </c>
@@ -1631,7 +1621,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="31"/>
+      <c r="A5" s="34"/>
       <c r="B5" s="9" t="s">
         <v>7</v>
       </c>
@@ -1682,7 +1672,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="32"/>
+      <c r="A6" s="35"/>
       <c r="B6" s="22" t="s">
         <v>8</v>
       </c>
@@ -1733,7 +1723,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="30">
+      <c r="A7" s="33">
         <f>A2+1</f>
         <v>2</v>
       </c>
@@ -1785,7 +1775,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="31"/>
+      <c r="A8" s="34"/>
       <c r="B8" s="9" t="s">
         <v>5</v>
       </c>
@@ -1835,7 +1825,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="31"/>
+      <c r="A9" s="34"/>
       <c r="B9" s="9" t="s">
         <v>6</v>
       </c>
@@ -1884,7 +1874,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="31"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="9" t="s">
         <v>7</v>
       </c>
@@ -1933,7 +1923,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="32"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="22" t="s">
         <v>8</v>
       </c>
@@ -1982,7 +1972,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="30">
+      <c r="A12" s="33">
         <f>A7+1</f>
         <v>3</v>
       </c>
@@ -2034,7 +2024,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="31"/>
+      <c r="A13" s="34"/>
       <c r="B13" s="9" t="s">
         <v>5</v>
       </c>
@@ -2084,7 +2074,7 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
+      <c r="A14" s="34"/>
       <c r="B14" s="9" t="s">
         <v>6</v>
       </c>
@@ -2133,7 +2123,7 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="31"/>
+      <c r="A15" s="34"/>
       <c r="B15" s="9" t="s">
         <v>7</v>
       </c>
@@ -2182,7 +2172,7 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="32"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="22" t="s">
         <v>8</v>
       </c>
@@ -2195,7 +2185,6 @@
       <c r="E16" s="14">
         <v>522.20000000000005</v>
       </c>
-      <c r="F16" s="35"/>
       <c r="G16" s="4">
         <v>15</v>
       </c>
@@ -2231,7 +2220,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="30">
+      <c r="A17" s="33">
         <f>A12+1</f>
         <v>4</v>
       </c>
@@ -2247,10 +2236,10 @@
       <c r="E17" s="18">
         <v>0.79</v>
       </c>
-      <c r="F17" s="36"/>
+      <c r="F17" s="15"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="31"/>
+      <c r="A18" s="34"/>
       <c r="B18" s="9" t="s">
         <v>5</v>
       </c>
@@ -2264,10 +2253,9 @@
       <c r="E18" s="12">
         <v>0</v>
       </c>
-      <c r="F18" s="35"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="31"/>
+      <c r="A19" s="34"/>
       <c r="B19" s="9" t="s">
         <v>6</v>
       </c>
@@ -2280,10 +2268,10 @@
       <c r="E19" s="20">
         <v>0.46100000000000002</v>
       </c>
-      <c r="F19" s="36"/>
+      <c r="F19" s="15"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="31"/>
+      <c r="A20" s="34"/>
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
@@ -2296,10 +2284,9 @@
       <c r="E20" s="12">
         <v>36.86</v>
       </c>
-      <c r="F20" s="35"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="32"/>
+      <c r="A21" s="35"/>
       <c r="B21" s="22" t="s">
         <v>8</v>
       </c>
@@ -2312,10 +2299,10 @@
       <c r="E21" s="23">
         <v>603.79999999999995</v>
       </c>
-      <c r="F21" s="37"/>
+      <c r="F21" s="3"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="30">
+      <c r="A22" s="33">
         <f>A17+1</f>
         <v>5</v>
       </c>
@@ -2331,10 +2318,10 @@
       <c r="E22" s="20">
         <v>0.80200000000000005</v>
       </c>
-      <c r="F22" s="36"/>
+      <c r="F22" s="15"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="31"/>
+      <c r="A23" s="34"/>
       <c r="B23" s="9" t="s">
         <v>5</v>
       </c>
@@ -2349,10 +2336,10 @@
       <c r="E23" s="19">
         <v>2</v>
       </c>
-      <c r="F23" s="38"/>
+      <c r="F23" s="30"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="31"/>
+      <c r="A24" s="34"/>
       <c r="B24" s="9" t="s">
         <v>6</v>
       </c>
@@ -2365,10 +2352,10 @@
       <c r="E24" s="20">
         <v>0.45600000000000002</v>
       </c>
-      <c r="F24" s="36"/>
+      <c r="F24" s="15"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="31"/>
+      <c r="A25" s="34"/>
       <c r="B25" s="9" t="s">
         <v>7</v>
       </c>
@@ -2381,10 +2368,10 @@
       <c r="E25" s="21">
         <v>37</v>
       </c>
-      <c r="F25" s="39"/>
+      <c r="F25" s="2"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="32"/>
+      <c r="A26" s="35"/>
       <c r="B26" s="22" t="s">
         <v>8</v>
       </c>
@@ -2397,10 +2384,10 @@
       <c r="E26" s="23">
         <v>555.6</v>
       </c>
-      <c r="F26" s="37"/>
+      <c r="F26" s="3"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="44" t="s">
+      <c r="A27" s="36" t="s">
         <v>23</v>
       </c>
       <c r="B27" s="9" t="s">
@@ -2418,10 +2405,10 @@
         <f>TEXT(AVERAGE(E2,E7,E12,E17,E22),"0.0" &amp; "%") &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(E2,E7,E12,E17,E22),"0.0" &amp; "%")</f>
         <v>78.2% ± 3.5%</v>
       </c>
-      <c r="F27" s="40"/>
+      <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="45"/>
+      <c r="A28" s="37"/>
       <c r="B28" s="9" t="s">
         <v>5</v>
       </c>
@@ -2437,10 +2424,10 @@
         <f>TEXT(AVERAGE(E3,E8,E13,E18,E23),"0.0" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(E3,E8,E13,E18,E23),"0.0")</f>
         <v>1.0 ± 1.4</v>
       </c>
-      <c r="F28" s="40"/>
+      <c r="F28" s="1"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="45"/>
+      <c r="A29" s="37"/>
       <c r="B29" s="9" t="s">
         <v>6</v>
       </c>
@@ -2456,10 +2443,10 @@
         <f>TEXT(AVERAGE(E4,E9,E14,E19,E24),"0.0" &amp; "%") &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(E4,E9,E14,E19,E24),"0.0" &amp; "%")</f>
         <v>45.0% ± 1.9%</v>
       </c>
-      <c r="F29" s="40"/>
+      <c r="F29" s="1"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
+      <c r="A30" s="37"/>
       <c r="B30" s="9" t="s">
         <v>7</v>
       </c>
@@ -2475,10 +2462,10 @@
         <f>TEXT(AVERAGE(E5,E10,E15,E20,E25),"0.00" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(E5,E10,E15,E20,E25),"0.00")</f>
         <v>35.68 ± 1.25</v>
       </c>
-      <c r="F30" s="40"/>
+      <c r="F30" s="1"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="45"/>
+      <c r="A31" s="37"/>
       <c r="B31" s="9" t="s">
         <v>8</v>
       </c>
@@ -2494,10 +2481,10 @@
         <f>TEXT(AVERAGE(E6,E11,E16,E21,E26),"0.0" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(E6,E11,E16,E21,E26),"0.0")</f>
         <v>559.3 ± 65.5</v>
       </c>
-      <c r="F31" s="40"/>
+      <c r="F31" s="1"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="45"/>
+      <c r="A32" s="37"/>
       <c r="B32" s="11" t="s">
         <v>22</v>
       </c>
@@ -2513,18 +2500,17 @@
         <f>TEXT(AVERAGE(P2:P6),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(P2:P6),"0.00%" )</f>
         <v>41.50% ± 4.63%</v>
       </c>
-      <c r="F32" s="35"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="45"/>
-      <c r="B33" s="41" t="s">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="37"/>
+      <c r="B33" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="35" t="str">
+      <c r="C33" t="str">
         <f>TEXT(AVERAGE(Q12:Q16),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(Q12:Q16),"0.00%" )</f>
         <v>44.02% ± 3.41%</v>
       </c>
-      <c r="D33" s="35" t="str">
+      <c r="D33" t="str">
         <f>TEXT(AVERAGE(Q7:Q11),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(Q7:Q11),"0.00%" )</f>
         <v>47.58% ± 6.06%</v>
       </c>
@@ -2532,31 +2518,30 @@
         <f>TEXT(AVERAGE(Q2:Q6),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(Q2:Q6),"0.00%" )</f>
         <v>47.76% ± 2.82%</v>
       </c>
-      <c r="F33" s="35"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="46"/>
-      <c r="B34" s="42" t="s">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="38"/>
+      <c r="B34" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="43">
-        <v>0.3</v>
-      </c>
-      <c r="D34" s="43">
-        <v>0.5</v>
-      </c>
-      <c r="E34" s="43">
-        <v>0.5</v>
+      <c r="D34" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="32" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A27:A34"/>
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A7:A11"/>
     <mergeCell ref="A12:A16"/>
     <mergeCell ref="A17:A21"/>
     <mergeCell ref="A22:A26"/>
-    <mergeCell ref="A27:A34"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2580,12 +2565,12 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="28"/>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
@@ -2605,7 +2590,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="34">
+      <c r="A3" s="40">
         <v>1</v>
       </c>
       <c r="B3" s="28" t="s">
@@ -2622,7 +2607,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="34"/>
+      <c r="A4" s="40"/>
       <c r="B4" s="28" t="s">
         <v>28</v>
       </c>
@@ -2639,7 +2624,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="34"/>
+      <c r="A5" s="40"/>
       <c r="B5" s="28" t="s">
         <v>27</v>
       </c>
@@ -2654,7 +2639,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="34"/>
+      <c r="A6" s="40"/>
       <c r="B6" s="28" t="s">
         <v>26</v>
       </c>
@@ -2669,7 +2654,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="34"/>
+      <c r="A7" s="40"/>
       <c r="B7" s="28" t="s">
         <v>25</v>
       </c>

--- a/覆盖率实验.xlsx
+++ b/覆盖率实验.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\Python\割草机导航\相机处理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC5F114-99DD-44E0-A1FC-63683C6C546E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB19975-7F05-445F-8073-DB4746C905BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{BB1149EE-BC81-4179-8825-480AF37C55DD}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{BB1149EE-BC81-4179-8825-480AF37C55DD}"/>
   </bookViews>
   <sheets>
     <sheet name="覆盖率实验" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="40">
   <si>
     <t>实验序号</t>
   </si>
@@ -161,6 +161,14 @@
   </si>
   <si>
     <t>成功率（人工估计）</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>E(视觉+改进+去重复场景)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>~10%</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -915,7 +923,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1011,6 +1019,15 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1020,20 +1037,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1391,27 +1444,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E43E82C4-08CF-414A-9FF9-5A529D6339BA}">
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.75" customWidth="1"/>
     <col min="4" max="4" width="12.4140625" customWidth="1"/>
-    <col min="5" max="6" width="12.58203125" customWidth="1"/>
-    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.4140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.9140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.58203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.58203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.25" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12.58203125" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.4140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.9140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.58203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" style="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.25" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1430,42 +1483,45 @@
       <c r="F1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="27" t="s">
+      <c r="Q1" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="27" t="s">
+      <c r="R1" s="27" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="33">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="36">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -1483,42 +1539,45 @@
       <c r="F2" s="18">
         <v>0.91400000000000003</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="18">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="H2" s="24">
         <v>1</v>
       </c>
-      <c r="H2" s="6">
+      <c r="I2" s="6">
         <v>1780476637.7119999</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="4">
+      <c r="L2" s="4">
         <v>1</v>
       </c>
-      <c r="L2" s="6">
+      <c r="M2" s="6">
         <v>89.39</v>
       </c>
-      <c r="M2" s="4">
+      <c r="N2" s="4">
         <v>154458</v>
       </c>
-      <c r="N2" s="4">
+      <c r="O2" s="4">
         <v>172800</v>
       </c>
-      <c r="O2" s="5">
+      <c r="P2" s="5">
         <v>722.7</v>
       </c>
-      <c r="P2" s="27">
+      <c r="Q2" s="27">
         <v>0.42399999999999999</v>
       </c>
-      <c r="Q2" s="27">
+      <c r="R2" s="27">
         <v>0.443</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="34"/>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="37"/>
       <c r="B3" s="9" t="s">
         <v>5</v>
       </c>
@@ -1535,42 +1594,45 @@
       <c r="F3" s="12">
         <v>5</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="12">
+        <v>0</v>
+      </c>
+      <c r="H3" s="24">
         <v>2</v>
       </c>
-      <c r="H3" s="6">
+      <c r="I3" s="6">
         <v>1780478348.4530001</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="4">
+      <c r="L3" s="4">
         <v>1</v>
       </c>
-      <c r="L3" s="6">
+      <c r="M3" s="6">
         <v>90.22</v>
       </c>
-      <c r="M3" s="4">
+      <c r="N3" s="4">
         <v>155892</v>
       </c>
-      <c r="N3" s="4">
+      <c r="O3" s="4">
         <v>172800</v>
       </c>
-      <c r="O3" s="5">
+      <c r="P3" s="5">
         <v>514.5</v>
       </c>
-      <c r="P3" s="27">
+      <c r="Q3" s="27">
         <v>0.40300000000000002</v>
       </c>
-      <c r="Q3" s="27">
+      <c r="R3" s="27">
         <v>0.47</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="34"/>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="37"/>
       <c r="B4" s="9" t="s">
         <v>6</v>
       </c>
@@ -1586,42 +1648,45 @@
       <c r="F4" s="20">
         <v>0.54500000000000004</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="20">
+        <v>0.57699999999999996</v>
+      </c>
+      <c r="H4" s="24">
         <v>3</v>
       </c>
-      <c r="H4" s="6">
+      <c r="I4" s="6">
         <v>1780489544.655</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="4">
+      <c r="L4" s="4">
         <v>1</v>
       </c>
-      <c r="L4" s="6">
+      <c r="M4" s="6">
         <v>88.3</v>
       </c>
-      <c r="M4" s="4">
+      <c r="N4" s="4">
         <v>152585</v>
       </c>
-      <c r="N4" s="4">
+      <c r="O4" s="4">
         <v>172800</v>
       </c>
-      <c r="O4" s="5">
+      <c r="P4" s="5">
         <v>554.5</v>
       </c>
-      <c r="P4" s="27">
+      <c r="Q4" s="27">
         <v>0.34300000000000003</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="R4" s="27">
         <v>0.46300000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="34"/>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="37"/>
       <c r="B5" s="9" t="s">
         <v>7</v>
       </c>
@@ -1637,42 +1702,45 @@
       <c r="F5" s="12">
         <v>50.41</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="12">
+        <v>44.79</v>
+      </c>
+      <c r="H5" s="24">
         <v>4</v>
       </c>
-      <c r="H5" s="6">
+      <c r="I5" s="6">
         <v>1780638632.1289999</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="4">
+      <c r="L5" s="4">
         <v>1</v>
       </c>
-      <c r="L5" s="6">
+      <c r="M5" s="6">
         <v>90.03</v>
       </c>
-      <c r="M5" s="4">
+      <c r="N5" s="4">
         <v>155566</v>
       </c>
-      <c r="N5" s="4">
+      <c r="O5" s="4">
         <v>172800</v>
       </c>
-      <c r="O5" s="5">
+      <c r="P5" s="5">
         <v>570.5</v>
       </c>
-      <c r="P5" s="27">
+      <c r="Q5" s="27">
         <v>0.439</v>
       </c>
-      <c r="Q5" s="27">
+      <c r="R5" s="27">
         <v>0.499</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="35"/>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="38"/>
       <c r="B6" s="22" t="s">
         <v>8</v>
       </c>
@@ -1688,42 +1756,45 @@
       <c r="F6" s="14">
         <v>673.4</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="14">
+        <v>774.2</v>
+      </c>
+      <c r="H6" s="24">
         <v>5</v>
       </c>
-      <c r="H6" s="6">
+      <c r="I6" s="6">
         <v>1780639418.529</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="K6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="4">
+      <c r="L6" s="4">
         <v>1</v>
       </c>
-      <c r="L6" s="6">
+      <c r="M6" s="6">
         <v>88.23</v>
       </c>
-      <c r="M6" s="4">
+      <c r="N6" s="4">
         <v>152464</v>
       </c>
-      <c r="N6" s="4">
+      <c r="O6" s="4">
         <v>172800</v>
       </c>
-      <c r="O6" s="5">
+      <c r="P6" s="5">
         <v>522.5</v>
       </c>
-      <c r="P6" s="27">
+      <c r="Q6" s="27">
         <v>0.46600000000000003</v>
       </c>
-      <c r="Q6" s="27">
+      <c r="R6" s="27">
         <v>0.51300000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="33">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="36">
         <f>A2+1</f>
         <v>2</v>
       </c>
@@ -1740,42 +1811,45 @@
         <v>0.82399999999999995</v>
       </c>
       <c r="F7" s="18"/>
-      <c r="G7" s="24">
+      <c r="G7" s="18">
+        <v>0.65</v>
+      </c>
+      <c r="H7" s="24">
         <v>6</v>
       </c>
-      <c r="H7" s="6">
+      <c r="I7" s="6">
         <v>1780643877.55</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="J7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="K7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K7" s="4">
+      <c r="L7" s="4">
         <v>1</v>
       </c>
-      <c r="L7" s="6">
+      <c r="M7" s="6">
         <v>89.12</v>
       </c>
-      <c r="M7" s="4">
+      <c r="N7" s="4">
         <v>153992</v>
       </c>
-      <c r="N7" s="4">
+      <c r="O7" s="4">
         <v>172800</v>
       </c>
-      <c r="O7" s="5">
+      <c r="P7" s="5">
         <v>636.6</v>
       </c>
-      <c r="P7" s="27">
+      <c r="Q7" s="27">
         <v>0.39500000000000002</v>
       </c>
-      <c r="Q7" s="27">
+      <c r="R7" s="27">
         <v>0.53100000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="34"/>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="37"/>
       <c r="B8" s="9" t="s">
         <v>5</v>
       </c>
@@ -1790,42 +1864,45 @@
         <v>0</v>
       </c>
       <c r="F8" s="12"/>
-      <c r="G8" s="24">
+      <c r="G8" s="12">
+        <v>0</v>
+      </c>
+      <c r="H8" s="24">
         <v>7</v>
       </c>
-      <c r="H8" s="6">
+      <c r="I8" s="6">
         <v>1780644902.7</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="K8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K8" s="4">
+      <c r="L8" s="4">
         <v>1</v>
       </c>
-      <c r="L8" s="6">
+      <c r="M8" s="6">
         <v>90.48</v>
       </c>
-      <c r="M8" s="4">
+      <c r="N8" s="4">
         <v>156351</v>
       </c>
-      <c r="N8" s="4">
+      <c r="O8" s="4">
         <v>172800</v>
       </c>
-      <c r="O8" s="5">
+      <c r="P8" s="5">
         <v>600.6</v>
       </c>
-      <c r="P8" s="27">
+      <c r="Q8" s="27">
         <v>0.41899999999999998</v>
       </c>
-      <c r="Q8" s="27">
+      <c r="R8" s="27">
         <v>0.54800000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="34"/>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="37"/>
       <c r="B9" s="9" t="s">
         <v>6</v>
       </c>
@@ -1839,42 +1916,45 @@
         <v>0.41599999999999998</v>
       </c>
       <c r="F9" s="20"/>
-      <c r="G9" s="24">
+      <c r="G9" s="20">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="H9" s="24">
         <v>8</v>
       </c>
-      <c r="H9" s="6">
+      <c r="I9" s="6">
         <v>1780657587.8050001</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="J9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="K9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="4">
+      <c r="L9" s="4">
         <v>1</v>
       </c>
-      <c r="L9" s="6">
+      <c r="M9" s="6">
         <v>92.8</v>
       </c>
-      <c r="M9" s="4">
+      <c r="N9" s="4">
         <v>160354</v>
       </c>
-      <c r="N9" s="4">
+      <c r="O9" s="4">
         <v>172800</v>
       </c>
-      <c r="O9" s="5">
+      <c r="P9" s="5">
         <v>558.6</v>
       </c>
-      <c r="P9" s="27">
+      <c r="Q9" s="27">
         <v>0.45900000000000002</v>
       </c>
-      <c r="Q9" s="27">
+      <c r="R9" s="27">
         <v>0.42299999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="34"/>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="37"/>
       <c r="B10" s="9" t="s">
         <v>7</v>
       </c>
@@ -1888,42 +1968,45 @@
         <v>35.42</v>
       </c>
       <c r="F10" s="12"/>
-      <c r="G10" s="24">
+      <c r="G10" s="12">
+        <v>39</v>
+      </c>
+      <c r="H10" s="24">
         <v>9</v>
       </c>
-      <c r="H10" s="6">
+      <c r="I10" s="6">
         <v>1780658903.9449999</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="J10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="K10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="4">
+      <c r="L10" s="4">
         <v>1</v>
       </c>
-      <c r="L10" s="6">
+      <c r="M10" s="6">
         <v>93.79</v>
       </c>
-      <c r="M10" s="4">
+      <c r="N10" s="4">
         <v>162061</v>
       </c>
-      <c r="N10" s="4">
+      <c r="O10" s="4">
         <v>172800</v>
       </c>
-      <c r="O10" s="5">
+      <c r="P10" s="5">
         <v>586.6</v>
       </c>
-      <c r="P10" s="27">
+      <c r="Q10" s="27">
         <v>0.49199999999999999</v>
       </c>
-      <c r="Q10" s="27">
+      <c r="R10" s="27">
         <v>0.41799999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="35"/>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="38"/>
       <c r="B11" s="22" t="s">
         <v>8</v>
       </c>
@@ -1937,42 +2020,45 @@
         <v>474.5</v>
       </c>
       <c r="F11" s="14"/>
-      <c r="G11" s="24">
+      <c r="G11" s="14">
+        <v>672.1</v>
+      </c>
+      <c r="H11" s="24">
         <v>10</v>
       </c>
-      <c r="H11" s="6">
+      <c r="I11" s="6">
         <v>1780663467.3629999</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="K11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="4">
+      <c r="L11" s="4">
         <v>1</v>
       </c>
-      <c r="L11" s="6">
+      <c r="M11" s="6">
         <v>89.43</v>
       </c>
-      <c r="M11" s="4">
+      <c r="N11" s="4">
         <v>154538</v>
       </c>
-      <c r="N11" s="4">
+      <c r="O11" s="4">
         <v>172800</v>
       </c>
-      <c r="O11" s="5">
+      <c r="P11" s="5">
         <v>586.5</v>
       </c>
-      <c r="P11" s="27">
+      <c r="Q11" s="27">
         <v>0.38700000000000001</v>
       </c>
-      <c r="Q11" s="27">
+      <c r="R11" s="27">
         <v>0.45900000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="33">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="36">
         <f>A7+1</f>
         <v>3</v>
       </c>
@@ -1988,43 +2074,46 @@
       <c r="E12" s="18">
         <v>0.73399999999999999</v>
       </c>
-      <c r="F12" s="18"/>
-      <c r="G12" s="4">
+      <c r="F12" s="48"/>
+      <c r="G12" s="18">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="H12" s="4">
         <v>11</v>
       </c>
-      <c r="H12" s="6">
+      <c r="I12" s="6">
         <v>1780732208.9449999</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="J12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="K12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="4">
+      <c r="L12" s="4">
         <v>1</v>
       </c>
-      <c r="L12" s="6">
+      <c r="M12" s="6">
         <v>95.5</v>
       </c>
-      <c r="M12" s="4">
+      <c r="N12" s="4">
         <v>165028</v>
       </c>
-      <c r="N12" s="4">
+      <c r="O12" s="4">
         <v>172800</v>
       </c>
-      <c r="O12" s="5">
+      <c r="P12" s="5">
         <v>482.4</v>
       </c>
-      <c r="P12" s="27">
+      <c r="Q12" s="27">
         <v>0.22900000000000001</v>
       </c>
-      <c r="Q12" s="27">
+      <c r="R12" s="27">
         <v>0.434</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="34"/>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="37"/>
       <c r="B13" s="9" t="s">
         <v>5</v>
       </c>
@@ -2038,43 +2127,46 @@
       <c r="E13" s="12">
         <v>0</v>
       </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="4">
+      <c r="F13" s="44"/>
+      <c r="G13" s="12">
+        <v>2</v>
+      </c>
+      <c r="H13" s="4">
         <v>12</v>
       </c>
-      <c r="H13" s="6">
+      <c r="I13" s="6">
         <v>1780733018.5020001</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="J13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="K13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K13" s="4">
+      <c r="L13" s="4">
         <v>1</v>
       </c>
-      <c r="L13" s="6">
+      <c r="M13" s="6">
         <v>98.98</v>
       </c>
-      <c r="M13" s="4">
+      <c r="N13" s="4">
         <v>171036</v>
       </c>
-      <c r="N13" s="4">
+      <c r="O13" s="4">
         <v>172800</v>
       </c>
-      <c r="O13" s="5">
+      <c r="P13" s="5">
         <v>510.5</v>
       </c>
-      <c r="P13" s="27">
+      <c r="Q13" s="27">
         <v>0.26</v>
       </c>
-      <c r="Q13" s="27">
+      <c r="R13" s="27">
         <v>0.45900000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="34"/>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="37"/>
       <c r="B14" s="9" t="s">
         <v>6</v>
       </c>
@@ -2087,43 +2179,46 @@
       <c r="E14" s="20">
         <v>0.46</v>
       </c>
-      <c r="F14" s="20"/>
-      <c r="G14" s="4">
+      <c r="F14" s="49"/>
+      <c r="G14" s="20">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="H14" s="4">
         <v>13</v>
       </c>
-      <c r="H14" s="6">
+      <c r="I14" s="6">
         <v>1780733949.013</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="J14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="K14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K14" s="4">
+      <c r="L14" s="4">
         <v>1</v>
       </c>
-      <c r="L14" s="6">
+      <c r="M14" s="6">
         <v>78.97</v>
       </c>
-      <c r="M14" s="4">
+      <c r="N14" s="4">
         <v>136465</v>
       </c>
-      <c r="N14" s="4">
+      <c r="O14" s="4">
         <v>172800</v>
       </c>
-      <c r="O14" s="5">
+      <c r="P14" s="5">
         <v>508.4</v>
       </c>
-      <c r="P14" s="27">
+      <c r="Q14" s="27">
         <v>0.3</v>
       </c>
-      <c r="Q14" s="27">
+      <c r="R14" s="27">
         <v>0.46300000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="34"/>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="37"/>
       <c r="B15" s="9" t="s">
         <v>7</v>
       </c>
@@ -2136,43 +2231,46 @@
       <c r="E15" s="12">
         <v>34.03</v>
       </c>
-      <c r="F15" s="12"/>
-      <c r="G15" s="4">
+      <c r="F15" s="44"/>
+      <c r="G15" s="12">
+        <v>43.49</v>
+      </c>
+      <c r="H15" s="4">
         <v>14</v>
       </c>
-      <c r="H15" s="6">
+      <c r="I15" s="6">
         <v>1780735036.589</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="J15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="K15" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K15" s="4">
+      <c r="L15" s="4">
         <v>1</v>
       </c>
-      <c r="L15" s="6">
+      <c r="M15" s="6">
         <v>99.94</v>
       </c>
-      <c r="M15" s="4">
+      <c r="N15" s="4">
         <v>172695</v>
       </c>
-      <c r="N15" s="4">
+      <c r="O15" s="4">
         <v>172800</v>
       </c>
-      <c r="O15" s="5">
+      <c r="P15" s="5">
         <v>466.4</v>
       </c>
-      <c r="P15" s="27">
+      <c r="Q15" s="27">
         <v>0.314</v>
       </c>
-      <c r="Q15" s="27">
+      <c r="R15" s="27">
         <v>0.46200000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="35"/>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="38"/>
       <c r="B16" s="22" t="s">
         <v>8</v>
       </c>
@@ -2185,42 +2283,46 @@
       <c r="E16" s="14">
         <v>522.20000000000005</v>
       </c>
-      <c r="G16" s="4">
+      <c r="F16" s="45"/>
+      <c r="G16" s="50">
+        <v>6.9929999999999994</v>
+      </c>
+      <c r="H16" s="4">
         <v>15</v>
       </c>
-      <c r="H16" s="6">
+      <c r="I16" s="6">
         <v>1780743171.9170001</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="J16" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="K16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="4">
+      <c r="L16" s="4">
         <v>1</v>
       </c>
-      <c r="L16" s="6">
+      <c r="M16" s="6">
         <v>99.81</v>
       </c>
-      <c r="M16" s="4">
+      <c r="N16" s="4">
         <v>172471</v>
       </c>
-      <c r="N16" s="4">
+      <c r="O16" s="4">
         <v>172800</v>
       </c>
-      <c r="O16" s="5">
+      <c r="P16" s="5">
         <v>580.5</v>
       </c>
-      <c r="P16" s="27">
+      <c r="Q16" s="27">
         <v>0.26700000000000002</v>
       </c>
-      <c r="Q16" s="27">
+      <c r="R16" s="27">
         <v>0.38300000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="33">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" s="36">
         <f>A12+1</f>
         <v>4</v>
       </c>
@@ -2236,10 +2338,46 @@
       <c r="E17" s="18">
         <v>0.79</v>
       </c>
-      <c r="F17" s="15"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="34"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48">
+        <v>0.67</v>
+      </c>
+      <c r="H17" s="4">
+        <v>16</v>
+      </c>
+      <c r="I17" s="6">
+        <v>1780817560.602</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L17" s="4">
+        <v>1</v>
+      </c>
+      <c r="M17" s="6">
+        <v>90.1</v>
+      </c>
+      <c r="N17" s="4">
+        <v>155691</v>
+      </c>
+      <c r="O17" s="4">
+        <v>172800</v>
+      </c>
+      <c r="P17" s="5">
+        <v>758.7</v>
+      </c>
+      <c r="Q17" s="27">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="R17" s="27">
+        <v>0.51900000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" s="37"/>
       <c r="B18" s="9" t="s">
         <v>5</v>
       </c>
@@ -2253,9 +2391,46 @@
       <c r="E18" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="34"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="52">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>17</v>
+      </c>
+      <c r="I18" s="6">
+        <v>1782216157.118</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L18" s="4">
+        <v>1</v>
+      </c>
+      <c r="M18" s="6">
+        <v>92.63</v>
+      </c>
+      <c r="N18" s="4">
+        <v>160072</v>
+      </c>
+      <c r="O18" s="4">
+        <v>172800</v>
+      </c>
+      <c r="P18" s="5">
+        <v>704.7</v>
+      </c>
+      <c r="Q18" s="27">
+        <v>0.152</v>
+      </c>
+      <c r="R18" s="27">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" s="37"/>
       <c r="B19" s="9" t="s">
         <v>6</v>
       </c>
@@ -2268,10 +2443,46 @@
       <c r="E19" s="20">
         <v>0.46100000000000002</v>
       </c>
-      <c r="F19" s="15"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="34"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="H19" s="4">
+        <v>18</v>
+      </c>
+      <c r="I19" s="6">
+        <v>1782217985.8800001</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L19" s="4">
+        <v>1</v>
+      </c>
+      <c r="M19" s="6">
+        <v>89.5</v>
+      </c>
+      <c r="N19" s="4">
+        <v>154650</v>
+      </c>
+      <c r="O19" s="4">
+        <v>172800</v>
+      </c>
+      <c r="P19" s="5">
+        <v>788.7</v>
+      </c>
+      <c r="Q19" s="27">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="R19" s="27">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" s="37"/>
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
@@ -2284,9 +2495,46 @@
       <c r="E20" s="12">
         <v>36.86</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="35"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="53">
+        <v>42.04</v>
+      </c>
+      <c r="H20" s="4">
+        <v>19</v>
+      </c>
+      <c r="I20" s="6">
+        <v>1782282789.5869999</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L20" s="4">
+        <v>1</v>
+      </c>
+      <c r="M20" s="6">
+        <v>91.11</v>
+      </c>
+      <c r="N20" s="4">
+        <v>157434</v>
+      </c>
+      <c r="O20" s="4">
+        <v>172800</v>
+      </c>
+      <c r="P20" s="5">
+        <v>710.7</v>
+      </c>
+      <c r="Q20" s="27">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="R20" s="27">
+        <v>0.48199999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" s="38"/>
       <c r="B21" s="22" t="s">
         <v>8</v>
       </c>
@@ -2299,10 +2547,46 @@
       <c r="E21" s="23">
         <v>603.79999999999995</v>
       </c>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="33">
+      <c r="F21" s="51"/>
+      <c r="G21" s="51">
+        <v>905.4</v>
+      </c>
+      <c r="H21" s="4">
+        <v>20</v>
+      </c>
+      <c r="I21" s="6">
+        <v>1782283668.029</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L21" s="4">
+        <v>1</v>
+      </c>
+      <c r="M21" s="6">
+        <v>88.22</v>
+      </c>
+      <c r="N21" s="4">
+        <v>152452</v>
+      </c>
+      <c r="O21" s="4">
+        <v>172800</v>
+      </c>
+      <c r="P21" s="5">
+        <v>756.7</v>
+      </c>
+      <c r="Q21" s="27">
+        <v>0.42099999999999999</v>
+      </c>
+      <c r="R21" s="27">
+        <v>0.40699999999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="36">
         <f>A17+1</f>
         <v>5</v>
       </c>
@@ -2319,9 +2603,45 @@
         <v>0.80200000000000005</v>
       </c>
       <c r="F22" s="15"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="34"/>
+      <c r="G22" s="48">
+        <v>0.80550100000000002</v>
+      </c>
+      <c r="H22" s="24">
+        <v>21</v>
+      </c>
+      <c r="I22" s="6">
+        <v>1782284724.596</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L22" s="4">
+        <v>1</v>
+      </c>
+      <c r="M22" s="6">
+        <v>92.71</v>
+      </c>
+      <c r="N22" s="4">
+        <v>160203</v>
+      </c>
+      <c r="O22" s="4">
+        <v>172800</v>
+      </c>
+      <c r="P22" s="5">
+        <v>940.9</v>
+      </c>
+      <c r="Q22" s="27">
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="R22" s="27">
+        <v>0.40699999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" s="37"/>
       <c r="B23" s="9" t="s">
         <v>5</v>
       </c>
@@ -2337,9 +2657,12 @@
         <v>2</v>
       </c>
       <c r="F23" s="30"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="34"/>
+      <c r="G23" s="54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" s="37"/>
       <c r="B24" s="9" t="s">
         <v>6</v>
       </c>
@@ -2353,9 +2676,12 @@
         <v>0.45600000000000002</v>
       </c>
       <c r="F24" s="15"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="34"/>
+      <c r="G24" s="49">
+        <v>0.46454200000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" s="37"/>
       <c r="B25" s="9" t="s">
         <v>7</v>
       </c>
@@ -2369,9 +2695,12 @@
         <v>37</v>
       </c>
       <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="35"/>
+      <c r="G25" s="55">
+        <v>37.745888999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A26" s="38"/>
       <c r="B26" s="22" t="s">
         <v>8</v>
       </c>
@@ -2385,9 +2714,12 @@
         <v>555.6</v>
       </c>
       <c r="F26" s="3"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="36" t="s">
+      <c r="G26" s="51">
+        <v>698.17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A27" s="33" t="s">
         <v>23</v>
       </c>
       <c r="B27" s="9" t="s">
@@ -2405,10 +2737,14 @@
         <f>TEXT(AVERAGE(E2,E7,E12,E17,E22),"0.0" &amp; "%") &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(E2,E7,E12,E17,E22),"0.0" &amp; "%")</f>
         <v>78.2% ± 3.5%</v>
       </c>
-      <c r="F27" s="1"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="42" t="str">
+        <f t="shared" ref="F27:G27" si="0">TEXT(AVERAGE(G2,G7,G12,G17,G22),"0.0" &amp; "%") &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(G2,G7,G12,G17,G22),"0.0" &amp; "%")</f>
+        <v>71.2% ± 6.6%</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A28" s="34"/>
       <c r="B28" s="9" t="s">
         <v>5</v>
       </c>
@@ -2424,10 +2760,14 @@
         <f>TEXT(AVERAGE(E3,E8,E13,E18,E23),"0.0" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(E3,E8,E13,E18,E23),"0.0")</f>
         <v>1.0 ± 1.4</v>
       </c>
-      <c r="F28" s="1"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="10" t="str">
+        <f t="shared" ref="F28:G28" si="1">TEXT(AVERAGE(G3,G8,G13,G18,G23),"0.0" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(G3,G8,G13,G18,G23),"0.0")</f>
+        <v>0.6 ± 0.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A29" s="34"/>
       <c r="B29" s="9" t="s">
         <v>6</v>
       </c>
@@ -2443,10 +2783,14 @@
         <f>TEXT(AVERAGE(E4,E9,E14,E19,E24),"0.0" &amp; "%") &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(E4,E9,E14,E19,E24),"0.0" &amp; "%")</f>
         <v>45.0% ± 1.9%</v>
       </c>
-      <c r="F29" s="1"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="37"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="10" t="str">
+        <f t="shared" ref="F29:G29" si="2">TEXT(AVERAGE(G4,G9,G14,G19,G24),"0.0" &amp; "%") &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(G4,G9,G14,G19,G24),"0.0" &amp; "%")</f>
+        <v>57.9% ± 7.2%</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A30" s="34"/>
       <c r="B30" s="9" t="s">
         <v>7</v>
       </c>
@@ -2462,10 +2806,14 @@
         <f>TEXT(AVERAGE(E5,E10,E15,E20,E25),"0.00" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(E5,E10,E15,E20,E25),"0.00")</f>
         <v>35.68 ± 1.25</v>
       </c>
-      <c r="F30" s="1"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="37"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="10" t="str">
+        <f t="shared" ref="F30:G30" si="3">TEXT(AVERAGE(G5,G10,G15,G20,G25),"0.00" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(G5,G10,G15,G20,G25),"0.00")</f>
+        <v>41.41 ± 2.97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A31" s="34"/>
       <c r="B31" s="9" t="s">
         <v>8</v>
       </c>
@@ -2481,46 +2829,60 @@
         <f>TEXT(AVERAGE(E6,E11,E16,E21,E26),"0.0" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(E6,E11,E16,E21,E26),"0.0")</f>
         <v>559.3 ± 65.5</v>
       </c>
-      <c r="F31" s="1"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="10" t="str">
+        <f t="shared" ref="F31:G31" si="4">TEXT(AVERAGE(G6,G11,G16,G21,G26),"0.0" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(G6,G11,G16,G21,G26),"0.0")</f>
+        <v>611.4 ± 349.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A32" s="34"/>
       <c r="B32" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C32" t="str">
-        <f>TEXT(AVERAGE(P12:P16),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(P12:P16),"0.00%" )</f>
+        <f>TEXT(AVERAGE(Q12:Q16),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(Q12:Q16),"0.00%" )</f>
         <v>27.40% ± 3.37%</v>
       </c>
       <c r="D32" t="str">
-        <f>TEXT(AVERAGE(P7:P11),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(P7:P11),"0.00%" )</f>
+        <f>TEXT(AVERAGE(Q7:Q11),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(Q7:Q11),"0.00%" )</f>
         <v>43.04% ± 4.44%</v>
       </c>
       <c r="E32" s="12" t="str">
-        <f>TEXT(AVERAGE(P2:P6),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(P2:P6),"0.00%" )</f>
+        <f>TEXT(AVERAGE(Q2:Q6),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(Q2:Q6),"0.00%" )</f>
         <v>41.50% ± 4.63%</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="12" t="str">
+        <f>TEXT(AVERAGE(Q17:Q22),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(Q17:Q22),"0.00%" )</f>
+        <v>30.33% ± 12.78%</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="34"/>
       <c r="B33" s="31" t="s">
         <v>17</v>
       </c>
       <c r="C33" t="str">
-        <f>TEXT(AVERAGE(Q12:Q16),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(Q12:Q16),"0.00%" )</f>
+        <f>TEXT(AVERAGE(R12:R16),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(R12:R16),"0.00%" )</f>
         <v>44.02% ± 3.41%</v>
       </c>
       <c r="D33" t="str">
-        <f>TEXT(AVERAGE(Q7:Q11),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(Q7:Q11),"0.00%" )</f>
+        <f>TEXT(AVERAGE(R7:R11),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(R7:R11),"0.00%" )</f>
         <v>47.58% ± 6.06%</v>
       </c>
       <c r="E33" s="12" t="str">
-        <f>TEXT(AVERAGE(Q2:Q6),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(Q2:Q6),"0.00%" )</f>
+        <f>TEXT(AVERAGE(R2:R6),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(R2:R6),"0.00%" )</f>
         <v>47.76% ± 2.82%</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="38"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="14" t="str">
+        <f>TEXT(AVERAGE(R17:R22),"0.00%" ) &amp; " ± " &amp; TEXT(_xlfn.STDEV.S(R17:R22),"0.00%" )</f>
+        <v>42.58% ± 6.13%</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="35"/>
       <c r="B34" s="4" t="s">
         <v>37</v>
       </c>
@@ -2532,6 +2894,13 @@
       </c>
       <c r="E34" s="32" t="s">
         <v>36</v>
+      </c>
+      <c r="F34" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="G34" s="47">
+        <f>3/7</f>
+        <v>0.42857142857142855</v>
       </c>
     </row>
   </sheetData>
@@ -2546,8 +2915,8 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C28:E28" formula="1"/>
-    <ignoredError sqref="D32:E33 C32:C33" formulaRange="1"/>
+    <ignoredError sqref="C28:E28 G28" formula="1"/>
+    <ignoredError sqref="D32:E33 C32:C33 G32:G33" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
